--- a/data/file_generation/input/data_57/2025-10-17_08_30_巴西甲_弗鲁米嫩塞[7]VS尤文图德[19]_标盘.xlsx
+++ b/data/file_generation/input/data_57/2025-10-17_08_30_巴西甲_弗鲁米嫩塞[7]VS尤文图德[19]_标盘.xlsx
@@ -13446,26 +13446,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B434912E-AAB0-41D6-95B9-A1C9ADFE6340}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86BC557D-07ED-4EA0-A5B4-208BB1EF0C55}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A02479-8D38-43B3-A24D-53D9D59C45C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61302FA0-B8E7-47BF-BF63-D0E2F882BCFF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7792B96-5001-40F0-B494-D5AD862E6A5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0507ED-5A91-49F3-A622-FDCD1E2363FA}"/>
 </file>